--- a/Documents/test_script.xlsx
+++ b/Documents/test_script.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="66">
   <si>
     <t>Test number</t>
   </si>
@@ -97,6 +97,126 @@
   </si>
   <si>
     <t>Error</t>
+  </si>
+  <si>
+    <t>Click "Contact Us" on navigation menu.</t>
+  </si>
+  <si>
+    <t>Display contact.jsp</t>
+  </si>
+  <si>
+    <t>contact.jsp displayed</t>
+  </si>
+  <si>
+    <t>Click on "Logout" when user logged in</t>
+  </si>
+  <si>
+    <t>Logout and direct to home page</t>
+  </si>
+  <si>
+    <t>Logged out and directed to home page</t>
+  </si>
+  <si>
+    <t>Click "HERE" to register</t>
+  </si>
+  <si>
+    <t>Taken to registration page</t>
+  </si>
+  <si>
+    <t>Click on "Come-in customer" on registration</t>
+  </si>
+  <si>
+    <t>Show customer registration form</t>
+  </si>
+  <si>
+    <t>Click on "Business customer" on registration</t>
+  </si>
+  <si>
+    <t>Show business registration form</t>
+  </si>
+  <si>
+    <t>Fill out customer registration page</t>
+  </si>
+  <si>
+    <t>Show success message</t>
+  </si>
+  <si>
+    <t>Fill out business registration page</t>
+  </si>
+  <si>
+    <t>Click on "My Account" when logged in as customer</t>
+  </si>
+  <si>
+    <t>Click on "My Account" when logged in as admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Click "Add to cart" button </t>
+  </si>
+  <si>
+    <t>Adds item to cart</t>
+  </si>
+  <si>
+    <t>Click "Checkout" on cart</t>
+  </si>
+  <si>
+    <t>PayPal login page</t>
+  </si>
+  <si>
+    <t>Click on create staff account in admin panel</t>
+  </si>
+  <si>
+    <t>Taken to staff registration</t>
+  </si>
+  <si>
+    <t>Fill out staff registration</t>
+  </si>
+  <si>
+    <t>Click on add service in admin panel</t>
+  </si>
+  <si>
+    <t>Taken to add service form</t>
+  </si>
+  <si>
+    <t>Fill out add service form correctly</t>
+  </si>
+  <si>
+    <t>Fill out add service form incorrectly (text for price)</t>
+  </si>
+  <si>
+    <t>Show error message</t>
+  </si>
+  <si>
+    <t>Click on update service in admin panel</t>
+  </si>
+  <si>
+    <t>Taken to update service form</t>
+  </si>
+  <si>
+    <t>Fill out update service form correctly</t>
+  </si>
+  <si>
+    <t>Fill out update service form incorreclty (text for price)</t>
+  </si>
+  <si>
+    <t>Click on delete service on admin panel</t>
+  </si>
+  <si>
+    <t>Taken to delete service form</t>
+  </si>
+  <si>
+    <t>Fill out delete service form</t>
+  </si>
+  <si>
+    <t>Click on view order history in admin panel</t>
+  </si>
+  <si>
+    <t>Shown order history</t>
+  </si>
+  <si>
+    <t>Login as customer, enter collection date and time and delivery date and time and press submit. Then login as admin and see if this is displayed on the view order history page</t>
+  </si>
+  <si>
+    <t>Update order history</t>
   </si>
 </sst>
 </file>
@@ -164,9 +284,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -502,13 +625,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="44.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -669,460 +792,391 @@
       <c r="A10">
         <v>9</v>
       </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
         <v>10</v>
       </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
         <v>11</v>
       </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
         <v>12</v>
       </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
         <v>13</v>
       </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
         <v>14</v>
       </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="B17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="B18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="B19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="B20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
+      <c r="B21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
+      <c r="B22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:1">
+      <c r="B23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:1">
+      <c r="B24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:1">
+      <c r="B25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:1">
+      <c r="B26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:1">
+      <c r="B27" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:1">
+      <c r="B28" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" t="s">
+        <v>54</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:1">
+      <c r="B29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" t="s">
+        <v>60</v>
+      </c>
+      <c r="E29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:1">
+      <c r="B30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:1">
+      <c r="B31" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" t="s">
+        <v>63</v>
+      </c>
+      <c r="E31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="60">
       <c r="A32">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65">
+      <c r="B32" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66">
+      <c r="C32" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1">
-      <c r="A91">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1">
-      <c r="A95">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1">
-      <c r="A98">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101">
-        <v>100</v>
+      <c r="D32" t="s">
+        <v>65</v>
+      </c>
+      <c r="E32" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
